--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/OKLAHOMA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/OKLAHOMA_2011.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C92">
@@ -2814,14 +2814,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C137">
         <v>47</v>
       </c>
       <c r="D137">
-        <v>0.009894736842105</v>
+        <v>0.009894736842105002</v>
       </c>
     </row>
     <row r="138">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C164">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C435">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C471">
